--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5B20D3-AFFA-4DC8-83E4-509ABE1ADF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9ED6C3-C093-4E69-9F99-87EE8EAB3333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33615" yWindow="3525" windowWidth="32745" windowHeight="13440" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="15645" yWindow="3630" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>id</t>
   </si>
@@ -48,7 +48,12 @@
     <t>text</t>
   </si>
   <si>
-    <t>화장실이 어디에 있나요?</t>
+    <t>중국 상하이 여행중 화장실이 마려울 때</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국어로 뭐라고 해야할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -560,7 +565,7 @@
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.25" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="50.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.875" customWidth="1"/>
@@ -574,10 +579,10 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>2</v>
@@ -615,6 +620,18 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
       <c r="H3" s="4"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9ED6C3-C093-4E69-9F99-87EE8EAB3333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3544A1-C03F-425C-8811-9E751B4B2DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15645" yWindow="3630" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-32490" yWindow="6420" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,11 +48,11 @@
     <t>text</t>
   </si>
   <si>
-    <t>중국 상하이 여행중 화장실이 마려울 때</t>
+    <t>중국 여행중 갑자기 급똥 신호가 왔을 때</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>중국어로 뭐라고 해야할까요?</t>
+    <t>어떤 중국어로 해결할 수 있을까요?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3544A1-C03F-425C-8811-9E751B4B2DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C7202-ACCA-4D18-9D04-E11716393B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32490" yWindow="6420" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-37710" yWindow="3570" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -53,6 +53,22 @@
   </si>
   <si>
     <t>어떤 중국어로 해결할 수 있을까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐라고 말해야 할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 여행중 맛있는 과일을 발견했다면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 여행중 과일이 먹고 싶은데</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀 더 싸게 먹고 싶다면?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -637,21 +653,69 @@
       <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:15">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="O7" s="4"/>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C7202-ACCA-4D18-9D04-E11716393B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F14207B-919E-4110-9C40-6F7CA5104793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37710" yWindow="3570" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="9930" yWindow="3240" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -69,6 +69,14 @@
   </si>
   <si>
     <t>좀 더 싸게 먹고 싶다면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이티 한 잔 마시러 왔다가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>길을 잃는 사람들을 위한 중국어</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -721,11 +729,35 @@
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="O9" s="4"/>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F14207B-919E-4110-9C40-6F7CA5104793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F33EFD-2B2B-4AB5-AC6F-F7418CC4EC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9930" yWindow="3240" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-33615" yWindow="3375" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -77,6 +77,10 @@
   </si>
   <si>
     <t>길을 잃는 사람들을 위한 중국어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸바오의 돌림자 '바오'를 알아보자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -791,6 +795,18 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:15">
+      <c r="A15">
+        <v>1000</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
     </row>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F33EFD-2B2B-4AB5-AC6F-F7418CC4EC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7F77EF-EAA3-49FB-BA99-327C2EE73FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33615" yWindow="3375" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -81,6 +81,10 @@
   </si>
   <si>
     <t>푸바오의 돌림자 '바오'를 알아보자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 초등학생들도 아는 한시를 알아보자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -811,6 +815,18 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:15">
+      <c r="A16">
+        <v>1001</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
     </row>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7F77EF-EAA3-49FB-BA99-327C2EE73FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34246176-3057-4AD0-ACC7-82CF19A29784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-33330" yWindow="4065" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -85,6 +85,14 @@
   </si>
   <si>
     <t>중국 초등학생들도 아는 한시를 알아보자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 미용실에서 머리 감다가 머리가 익을 것 같다면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 미용실에서 장원영 스타일로 머리를 자르고 싶다면?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -771,13 +779,35 @@
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="D10" s="9"/>
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="D11" s="9"/>
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="O11" s="4"/>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34246176-3057-4AD0-ACC7-82CF19A29784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038F5351-9734-4AE9-A73B-556F6DA8D4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33330" yWindow="4065" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-29745" yWindow="2115" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>id</t>
   </si>
@@ -93,6 +93,10 @@
   </si>
   <si>
     <t>중국 미용실에서 장원영 스타일로 머리를 자르고 싶다면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국인도 존경하는 한국인 장군의 한시를 알아보자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -860,51 +864,63 @@
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="4:13">
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>1002</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="4:13">
+    <row r="18" spans="1:13">
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
     </row>
-    <row r="19" spans="4:13">
+    <row r="19" spans="1:13">
       <c r="D19" s="9"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
     </row>
-    <row r="20" spans="4:13">
+    <row r="20" spans="1:13">
       <c r="D20" s="6"/>
       <c r="E20" s="10"/>
       <c r="G20" s="4"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="4:13">
+    <row r="21" spans="1:13">
       <c r="D21" s="6"/>
       <c r="E21" s="10"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="4:13">
+    <row r="22" spans="1:13">
       <c r="D22" s="6"/>
       <c r="E22" s="10"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="4:13">
+    <row r="23" spans="1:13">
       <c r="D23" s="6"/>
       <c r="E23" s="10"/>
     </row>
-    <row r="25" spans="4:13">
+    <row r="25" spans="1:13">
       <c r="E25" s="10"/>
     </row>
-    <row r="26" spans="4:13">
+    <row r="26" spans="1:13">
       <c r="E26" s="10"/>
     </row>
-    <row r="27" spans="4:13">
+    <row r="27" spans="1:13">
       <c r="E27" s="10"/>
     </row>
-    <row r="28" spans="4:13">
+    <row r="28" spans="1:13">
       <c r="E28" s="10"/>
     </row>
     <row r="33" spans="5:7">

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038F5351-9734-4AE9-A73B-556F6DA8D4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2BB70E-0EC9-410F-BC1F-7220679C9151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29745" yWindow="2115" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-22425" yWindow="3465" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>중국인도 존경하는 한국인 장군의 한시를 알아보자</t>
+    <t>중국인들도 존경한 조선 명장의 시를 중국어로 읊어보자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2BB70E-0EC9-410F-BC1F-7220679C9151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1650BD25-087E-4A12-A2BA-27C25B176E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22425" yWindow="3465" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-31470" yWindow="2595" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,69 +34,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>set_id</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>중국 여행중 갑자기 급똥 신호가 왔을 때</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 중국어로 해결할 수 있을까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐라고 말해야 할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 여행중 맛있는 과일을 발견했다면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 여행중 과일이 먹고 싶은데</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀 더 싸게 먹고 싶다면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이티 한 잔 마시러 왔다가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>길을 잃는 사람들을 위한 중국어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸바오의 돌림자 '바오'를 알아보자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 초등학생들도 아는 한시를 알아보자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 미용실에서 머리 감다가 머리가 익을 것 같다면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 미용실에서 장원영 스타일로 머리를 자르고 싶다면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국인들도 존경한 조선 명장의 시를 중국어로 읊어보자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>seq</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>set_id</t>
-  </si>
-  <si>
-    <t>seq</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>중국 여행중 갑자기 급똥 신호가 왔을 때</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>어떤 중국어로 해결할 수 있을까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭐라고 말해야 할까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국 여행중 맛있는 과일을 발견했다면</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국 여행중 과일이 먹고 싶은데</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>좀 더 싸게 먹고 싶다면?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤이티 한 잔 마시러 왔다가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>길을 잃는 사람들을 위한 중국어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>푸바오의 돌림자 '바오'를 알아보자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국 초등학생들도 아는 한시를 알아보자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국 미용실에서 머리 감다가 머리가 익을 것 같다면?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국 미용실에서 장원영 스타일로 머리를 자르고 싶다면?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국인들도 존경한 조선 명장의 시를 중국어로 읊어보자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>양꼬치 먹을 때 이것 때문에 못 먹는 사람들은?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">중국에서 향신료 때문에 음식을 거른 적이 있다면 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 말을 연습해보자!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국인이라면 이건 더 달라고 해야죠?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -623,16 +641,16 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -656,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2"/>
       <c r="L2" s="8"/>
@@ -668,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3" s="4"/>
       <c r="M3" s="8"/>
@@ -691,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -702,13 +720,13 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
@@ -725,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
@@ -736,13 +754,13 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
@@ -759,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -770,13 +788,13 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
@@ -793,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
@@ -810,73 +828,83 @@
         <v>1</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="D12" s="9"/>
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="D13" s="9"/>
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="D14" s="5"/>
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>12</v>
+      <c r="D15" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16">
-        <v>1001</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17">
-        <v>1002</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
+      <c r="D17" s="5"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
     </row>
@@ -921,7 +949,47 @@
       <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:13">
+      <c r="A28">
+        <v>1000</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
       <c r="E28" s="10"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29">
+        <v>1001</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30">
+        <v>1002</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="33" spans="5:7">
       <c r="G33" s="6"/>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,11 +429,6 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>seq</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>text</t>
         </is>
       </c>
@@ -451,12 +446,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>중국 여행중 갑자기 급똥 신호가 왔을 때</t>
+          <t>중국 여행중 갑자기 급똥 신호가 왔을 때
+어떤 중국어로 해결할 수 있을까요?</t>
         </is>
       </c>
     </row>
@@ -468,17 +459,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>어떤 중국어로 해결할 수 있을까요?</t>
+          <t>중국 여행중 맛있는 과일을 발견했다면
+뭐라고 말해야 할까요?</t>
         </is>
       </c>
     </row>
@@ -490,17 +477,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>중국 여행중 맛있는 과일을 발견했다면</t>
+          <t>중국 여행중 과일이 먹고 싶은데
+좀 더 싸게 먹고 싶다면?</t>
         </is>
       </c>
     </row>
@@ -512,17 +495,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>뭐라고 말해야 할까요?</t>
+          <t>헤이티 한 잔 마시러 왔다가
+길을 잃는 사람들을 위한 중국어</t>
         </is>
       </c>
     </row>
@@ -534,17 +513,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>중국 여행중 과일이 먹고 싶은데</t>
+          <t>중국 미용실에서 머리 감다가 머리가 익을 것 같다면?</t>
         </is>
       </c>
     </row>
@@ -556,17 +530,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>좀 더 싸게 먹고 싶다면?</t>
+          <t>중국 미용실에서 장원영 스타일로 머리를 자르고 싶다면?</t>
         </is>
       </c>
     </row>
@@ -578,61 +547,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>헤이티 한 잔 마시러 왔다가</t>
+          <t>고수향을 싫어하는 사람들은
+이 말을 기억하세요</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>길을 잃는 사람들을 위한 중국어</t>
+          <t>양꼬치 먹을 때 이것 때문에 못 먹는 사람들은?</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>중국 미용실에서 머리 감다가 머리가 익을 것 같다면?</t>
+          <t>한국 사람이라면 이건 많이 넣어달라고 해야해요</t>
         </is>
       </c>
     </row>
@@ -644,241 +599,148 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>중국 미용실에서 장원영 스타일로 머리를 자르고 싶다면?</t>
+          <t>무더운 여름, 중국 식당에 들어왔는데
+따뜻한 물이 나와 당황했다면?</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>고수향을 싫어하는 사람들은</t>
+          <t>마라탕같이 빨간 국물이 옷에 튀지 않게 하려면?</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>이 말을 기억하세요</t>
+          <t>칭다오, 하얼빈 같은 중국 맥주도 먹어봐야겠죠?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>양꼬치 먹을 때 이것 때문에 못 먹는 사람들은?</t>
+          <t>중국 식당에서 음식을 다 먹고 카운터 앞에서
+결제를 하려면 이렇게 말해보세요</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>카카오페이에서 지원되는 알리페이를 사용하려면?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>한국 사람이라면 이건 많이 넣어달라고 해야해요</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>위챗 계정으로 위챗페이를 쓸 수 있다면?</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>푸바오의 돌림자 '바오'를 알아보자</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>중국 초등학생들도 아는 한시를 알아보자</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>푸바오의 돌림자 '바오'를 알아보자</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>중국 초등학생들도 아는 한시를 알아보자</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>중국인들도 존경한 조선 명장의 시를 중국어로 읊어보자</t>
         </is>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -742,7 +742,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>중국인들도 존경한 조선 명장의 시를 중국어로 읊어보자</t>
+          <t>중국인들도 존경하는 조선 시대 명장이 남긴
+한시를 중국어로 알아보자</t>
         </is>
       </c>
     </row>

--- a/resource/table/ko_narration_lines.xlsx
+++ b/resource/table/ko_narration_lines.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>중국인들도 존경하는 조선 시대 명장이 남긴
+          <t>중국인들도 존경하는 한국의 명장이 남긴
 한시를 중국어로 알아보자</t>
         </is>
       </c>
